--- a/sam_themes_palette_review.xlsx
+++ b/sam_themes_palette_review.xlsx
@@ -66,17 +66,17 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="94">
+  <fills count="93">
     <fill>
       <patternFill/>
     </fill>
@@ -95,12 +95,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CBA14C"/>
+        <fgColor rgb="005B84B1"/>
       </patternFill>
     </fill>
     <fill>
@@ -120,7 +115,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D49850"/>
+        <fgColor rgb="007EC9A0"/>
       </patternFill>
     </fill>
     <fill>
@@ -150,7 +145,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C5402F"/>
+        <fgColor rgb="00B23D2C"/>
       </patternFill>
     </fill>
     <fill>
@@ -160,7 +155,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D7A83C"/>
+        <fgColor rgb="00E08F2E"/>
       </patternFill>
     </fill>
     <fill>
@@ -170,7 +165,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B0803E"/>
+        <fgColor rgb="008A8058"/>
       </patternFill>
     </fill>
     <fill>
@@ -190,7 +185,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D94040"/>
+        <fgColor rgb="00CF3550"/>
       </patternFill>
     </fill>
     <fill>
@@ -200,7 +195,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D49858"/>
+        <fgColor rgb="00B8703A"/>
       </patternFill>
     </fill>
     <fill>
@@ -220,7 +215,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C47830"/>
+        <fgColor rgb="009A7BA0"/>
       </patternFill>
     </fill>
     <fill>
@@ -270,7 +265,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D89858"/>
+        <fgColor rgb="003F8F94"/>
       </patternFill>
     </fill>
     <fill>
@@ -280,22 +275,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D2A24A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002A1820"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9A441"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00171410"/>
+        <fgColor rgb="00C17858"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00341524"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008F6FD4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00160F24"/>
       </patternFill>
     </fill>
     <fill>
@@ -330,7 +325,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D08A45"/>
+        <fgColor rgb="007A8FA3"/>
       </patternFill>
     </fill>
     <fill>
@@ -340,7 +335,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2537F"/>
+        <fgColor rgb="00D15F82"/>
       </patternFill>
     </fill>
     <fill>
@@ -350,7 +345,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D63A33"/>
+        <fgColor rgb="00C94A1E"/>
       </patternFill>
     </fill>
     <fill>
@@ -390,7 +385,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8A050"/>
+        <fgColor rgb="00C98868"/>
       </patternFill>
     </fill>
     <fill>
@@ -400,17 +395,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C89060"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00241A14"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D8A24E"/>
+        <fgColor rgb="0063788A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001C2228"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009FB8C9"/>
       </patternFill>
     </fill>
     <fill>
@@ -430,6 +425,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="004FA0A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E2622A"/>
       </patternFill>
     </fill>
@@ -460,7 +460,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C98A3E"/>
+        <fgColor rgb="00C17F34"/>
       </patternFill>
     </fill>
     <fill>
@@ -470,7 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D34338"/>
+        <fgColor rgb="009C3F2A"/>
       </patternFill>
     </fill>
     <fill>
@@ -480,7 +480,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8783C"/>
+        <fgColor rgb="007A9468"/>
       </patternFill>
     </fill>
     <fill>
@@ -490,7 +490,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B87A3E"/>
+        <fgColor rgb="009C6F38"/>
       </patternFill>
     </fill>
     <fill>
@@ -500,7 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DFB23C"/>
+        <fgColor rgb="00E0B840"/>
       </patternFill>
     </fill>
     <fill>
@@ -510,7 +510,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C7995A"/>
+        <fgColor rgb="00E2C48F"/>
       </patternFill>
     </fill>
     <fill>
@@ -520,17 +520,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CDA24F"/>
+        <fgColor rgb="00A8ADB8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0015192A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C69A4B"/>
       </patternFill>
     </fill>
     <fill>
@@ -556,7 +551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -567,45 +562,33 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -621,10 +604,10 @@
     <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -633,10 +616,10 @@
     <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -645,13 +628,13 @@
     <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -663,10 +646,10 @@
     <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -693,19 +676,19 @@
     <xf numFmtId="0" fontId="8" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="40" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="40" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -717,34 +700,34 @@
     <xf numFmtId="0" fontId="8" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="46" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="47" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="48" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="50" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="46" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="47" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="48" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="50" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="51" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="53" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="54" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="55" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="53" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="54" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="55" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="56" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -771,7 +754,7 @@
     <xf numFmtId="0" fontId="8" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -783,82 +766,79 @@
     <xf numFmtId="0" fontId="8" fillId="67" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="68" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="69" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="70" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="71" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="72" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="73" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="74" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="75" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="76" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="68" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="69" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="70" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="71" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="72" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="73" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="74" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="75" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="76" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="77" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="78" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="79" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="80" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="81" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="82" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="83" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="84" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="85" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="86" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="87" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="88" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="89" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="90" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="78" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="79" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="80" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="81" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="82" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="83" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="84" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="85" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="86" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="87" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="88" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="89" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="90" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="91" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="92" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="93" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="92" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1304,41 +1284,41 @@
           <t>Gary</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>《登龙妙招》
 Strictly Business · 1991</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>#CBA14C</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>天际铜金
-Skyline Brass</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>#5B84B1</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>天际钢蓝
+Skyline Steel</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>#14110D</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>顶楼黑檀
 Penthouse Ebony</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr"/>
+      <c r="H4" s="9" t="inlineStr"/>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Krzysztof "Kris" Wilk</t>
         </is>
@@ -1349,29 +1329,29 @@
 Somebody to Love · 1994</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>#BC4D3A</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>余烬绯红
 Ember Cardinal</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>#11161C</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>华沙墨蓝
 Warsaw Indigo</t>
         </is>
       </c>
-      <c r="H5" s="16" t="inlineStr"/>
+      <c r="H5" s="9" t="inlineStr"/>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -1382,41 +1362,41 @@
           <t>Matty</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>《宽恕》
 Mercy · 1995</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>#D49850</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>旧电话亭琥珀
-Old Phonebooth Amber</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>#7EC9A0</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>旧电话亭荧光
+Booth Fluorescent</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>#171D24</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>凌晨地铁月台
 Pre-Dawn Subway</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr"/>
+      <c r="H6" s="9" t="inlineStr"/>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Buck "The Kid"</t>
         </is>
@@ -1427,35 +1407,35 @@
 Box of Moonlight · 1996</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>#B8C878</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>林间苔绿
 Forest Moss</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>#1A2418</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>月光银白
 Moonlight Silver</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr"/>
+      <c r="H7" s="9" t="inlineStr"/>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Trent</t>
         </is>
@@ -1466,29 +1446,29 @@
 Lawn Dogs · 1997</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>#79A7BD</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>天蓝卡车
 Pickup Sky</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>#141C12</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>新刈草青
 Mown Lawn</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr"/>
+      <c r="H8" s="9" t="inlineStr"/>
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="4" t="n">
@@ -1499,35 +1479,35 @@
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>《冒牌高手》
 Safe Men · 1998</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>#C5402F</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>舞台背心红
-Stage Vest</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>#B23D2C</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>复古戏服红
+Vintage Costume Red</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>#211A0F</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>格纹芥末棕
 Plaid Mustard</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr"/>
+      <c r="H9" s="9" t="inlineStr"/>
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -1538,35 +1518,35 @@
           <t>Jerry</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>《师徒杀手闯江湖》
 Jerry and Tom · 1998</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
-        <is>
-          <t>#D7A83C</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>蓬乱金长发
-Blond Mane</t>
-        </is>
-      </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>#E08F2E</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>金毛薯条橙
+Fry Basket Orange</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>#20120C</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>深夜快餐棕
 Late-Night Diner</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr"/>
+      <c r="H10" s="9" t="inlineStr"/>
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="4" t="n">
@@ -1577,41 +1557,41 @@
           <t>William "Wild Bill" Wharton</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>《绿里奇迹》
 The Green Mile · 1999</t>
         </is>
       </c>
-      <c r="D11" s="27" t="inlineStr">
-        <is>
-          <t>#B0803E</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>锯末粗木
-Sawdust Timber</t>
-        </is>
-      </c>
-      <c r="F11" s="28" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>#8A8058</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>锯木原色
+Raw Timber</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>#1B1510</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>炉膛夜黑
 Forge Soot</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr"/>
+      <c r="H11" s="9" t="inlineStr"/>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Guy Fleegman</t>
         </is>
@@ -1622,29 +1602,29 @@
 Galaxy Quest · 1999</t>
         </is>
       </c>
-      <c r="D12" s="29" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>#43B3BF</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>控制台青
 Console Teal</t>
         </is>
       </c>
-      <c r="F12" s="30" t="inlineStr">
+      <c r="F12" s="25" t="inlineStr">
         <is>
           <t>#0F161A</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>深空黛黑
 Deep-Space Black</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr"/>
+      <c r="H12" s="9" t="inlineStr"/>
     </row>
     <row r="13" ht="54" customHeight="1">
       <c r="A13" s="4" t="n">
@@ -1655,35 +1635,35 @@
           <t>Eric Knox</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>《霹雳娇娃》
 Charlie's Angels · 2000</t>
         </is>
       </c>
-      <c r="D13" s="31" t="inlineStr">
-        <is>
-          <t>#D94040</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>红镜红
-Crimson Lens</t>
-        </is>
-      </c>
-      <c r="F13" s="32" t="inlineStr">
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>#CF3550</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>镜绯红
+Rouge Lens</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="inlineStr">
         <is>
           <t>#1B1310</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>可乐棕
 Cola Noir</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr"/>
+      <c r="H13" s="9" t="inlineStr"/>
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="4" t="n">
@@ -1694,41 +1674,41 @@
           <t>Pero "Pepe" Mahalovic</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>《欢迎来到科林伍德》
 Welcome to Collinwood · 2002</t>
         </is>
       </c>
-      <c r="D14" s="33" t="inlineStr">
-        <is>
-          <t>#D49858</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>拳击台暖灯橘
-Ring Lamp Amber</t>
-        </is>
-      </c>
-      <c r="F14" s="34" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>#B8703A</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>拳击场铁锈橘
+Ring Rust</t>
+        </is>
+      </c>
+      <c r="F14" s="29" t="inlineStr">
         <is>
           <t>#1A1612</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>科林伍德暮色
 Collinwood Dusk</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr"/>
+      <c r="H14" s="9" t="inlineStr"/>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Chuck Barris</t>
         </is>
@@ -1739,29 +1719,29 @@
 Confessions of a Dangerous Mind · 2002</t>
         </is>
       </c>
-      <c r="D15" s="35" t="inlineStr">
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>#DE6E8E</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>镁光节目粉
 Limelight Pink</t>
         </is>
       </c>
-      <c r="F15" s="36" t="inlineStr">
+      <c r="F15" s="31" t="inlineStr">
         <is>
           <t>#15182A</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>午夜情报蓝
 Midnight Spy</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
     </row>
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="4" t="n">
@@ -1772,41 +1752,41 @@
           <t>Frank Mercer</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>《火柴人》
 Matchstick Men · 2003</t>
         </is>
       </c>
-      <c r="D16" s="37" t="inlineStr">
-        <is>
-          <t>#C47830</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>猫眼琥珀
-Hazel Fox</t>
-        </is>
-      </c>
-      <c r="F16" s="38" t="inlineStr">
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>#9A7BA0</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>银灰猫眼
+Mauve Fox</t>
+        </is>
+      </c>
+      <c r="F16" s="33" t="inlineStr">
         <is>
           <t>#1A1410</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>焦黑火柴
 Burnt Matchstick</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr"/>
+      <c r="H16" s="9" t="inlineStr"/>
     </row>
     <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Jim Crocker</t>
         </is>
@@ -1817,35 +1797,35 @@
 Piccadilly Jim · 2004</t>
         </is>
       </c>
-      <c r="D17" s="39" t="inlineStr">
+      <c r="D17" s="34" t="inlineStr">
         <is>
           <t>#D8B25A</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>夜会香槟金
 Club Champagne</t>
         </is>
       </c>
-      <c r="F17" s="40" t="inlineStr">
+      <c r="F17" s="35" t="inlineStr">
         <is>
           <t>#161214</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>黑貂皮大氅
 Mink Black</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr"/>
+      <c r="H17" s="9" t="inlineStr"/>
     </row>
     <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Zaphod Beeblebrox</t>
         </is>
@@ -1856,35 +1836,35 @@
 The Hitchhiker's Guide to the Galaxy · 2005</t>
         </is>
       </c>
-      <c r="D18" s="41" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>#D4A82A</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>总统鬃金
 President's Mane</t>
         </is>
       </c>
-      <c r="F18" s="42" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>#0B0A12</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>黑甲漆夜
 Lacquer Black</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr"/>
+      <c r="H18" s="9" t="inlineStr"/>
     </row>
     <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Brad Cairn</t>
         </is>
@@ -1895,35 +1875,35 @@
 Joshua · 2007</t>
         </is>
       </c>
-      <c r="D19" s="43" t="inlineStr">
+      <c r="D19" s="38" t="inlineStr">
         <is>
           <t>#C9D84E</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>网球荧光黄
 Tennis Ball</t>
         </is>
       </c>
-      <c r="F19" s="44" t="inlineStr">
+      <c r="F19" s="39" t="inlineStr">
         <is>
           <t>#1C2230</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>曼哈顿冬夜
 Manhattan Slate</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr"/>
+      <c r="H19" s="9" t="inlineStr"/>
     </row>
     <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Glenn Marchand</t>
         </is>
@@ -1934,29 +1914,29 @@
 Snow Angels · 2007</t>
         </is>
       </c>
-      <c r="D20" s="45" t="inlineStr">
+      <c r="D20" s="40" t="inlineStr">
         <is>
           <t>#B8D0E0</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>初雪微光白
 First Snow</t>
         </is>
       </c>
-      <c r="F20" s="46" t="inlineStr">
+      <c r="F20" s="41" t="inlineStr">
         <is>
           <t>#1C2030</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>寒冬冷蓝灰
 Winter Steel</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr"/>
+      <c r="H20" s="9" t="inlineStr"/>
     </row>
     <row r="21" ht="54" customHeight="1">
       <c r="A21" s="4" t="n">
@@ -1967,35 +1947,35 @@
           <t>Jim Reston</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>《福斯特对话尼克松》
 Frost/Nixon · 2008</t>
         </is>
       </c>
-      <c r="D21" s="47" t="inlineStr">
-        <is>
-          <t>#D89858</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>钨丝暖灯金
-Tungsten Glow</t>
-        </is>
-      </c>
-      <c r="F21" s="48" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
+        <is>
+          <t>#3F8F94</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>演播室蓝光
+Studio Cathode Blue</t>
+        </is>
+      </c>
+      <c r="F21" s="43" t="inlineStr">
         <is>
           <t>#1F1814</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>深夜手稿棕
 Manuscript Brown</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr"/>
+      <c r="H21" s="9" t="inlineStr"/>
     </row>
     <row r="22" ht="54" customHeight="1">
       <c r="A22" s="4" t="n">
@@ -2006,35 +1986,35 @@
           <t>Victor Mancini</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>《窒色》
 Choke · 2008</t>
         </is>
       </c>
-      <c r="D22" s="49" t="inlineStr">
-        <is>
-          <t>#D2A24A</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>殖民地铜金
-Colonial Gilt</t>
-        </is>
-      </c>
-      <c r="F22" s="50" t="inlineStr">
-        <is>
-          <t>#2A1820</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>旧绒布酒红
-Velvet Wine</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr"/>
+      <c r="D22" s="44" t="inlineStr">
+        <is>
+          <t>#C17858</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>铜锈玫瑰
+Copper Rose</t>
+        </is>
+      </c>
+      <c r="F22" s="45" t="inlineStr">
+        <is>
+          <t>#341524</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>绒夜玫红
+Rose Velvet Night</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr"/>
     </row>
     <row r="23" ht="54" customHeight="1">
       <c r="A23" s="4" t="n">
@@ -2045,41 +2025,41 @@
           <t>Bronco</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>《绅士布朗科》
 Gentlemen Broncos · 2009</t>
         </is>
       </c>
-      <c r="D23" s="51" t="inlineStr">
-        <is>
-          <t>#D9A441</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>蜂蜜琥珀
-Honey Amber</t>
-        </is>
-      </c>
-      <c r="F23" s="52" t="inlineStr">
-        <is>
-          <t>#171410</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>纸页暮褐
-Paperback Dusk</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr"/>
+      <c r="D23" s="46" t="inlineStr">
+        <is>
+          <t>#8F6FD4</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>星际紫晶
+Cosmic Violet</t>
+        </is>
+      </c>
+      <c r="F23" s="47" t="inlineStr">
+        <is>
+          <t>#160F24</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>星尘墨夜
+Stardust Night</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr"/>
     </row>
     <row r="24" ht="54" customHeight="1">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Sam Bell</t>
         </is>
@@ -2090,29 +2070,29 @@
 Moon · 2009</t>
         </is>
       </c>
-      <c r="D24" s="53" t="inlineStr">
+      <c r="D24" s="48" t="inlineStr">
         <is>
           <t>#7EB0D5</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>基地微光
 Sarang Glow</t>
         </is>
       </c>
-      <c r="F24" s="54" t="inlineStr">
+      <c r="F24" s="49" t="inlineStr">
         <is>
           <t>#162038</t>
         </is>
       </c>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>月球蔚蓝
 Lunar Blue</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr"/>
+      <c r="H24" s="9" t="inlineStr"/>
     </row>
     <row r="25" ht="54" customHeight="1">
       <c r="A25" s="4" t="n">
@@ -2123,41 +2103,41 @@
           <t>Robert Goode</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>《天伦之旅》
 Everybody's Fine · 2009</t>
         </is>
       </c>
-      <c r="D25" s="55" t="inlineStr">
+      <c r="D25" s="50" t="inlineStr">
         <is>
           <t>#CC4436</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>圣诞帽红
 Santa Hat</t>
         </is>
       </c>
-      <c r="F25" s="56" t="inlineStr">
+      <c r="F25" s="51" t="inlineStr">
         <is>
           <t>#211910</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>鼓皮深棕
 Drumskin Brown</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr"/>
+      <c r="H25" s="9" t="inlineStr"/>
     </row>
     <row r="26" ht="54" customHeight="1">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Justin Hammer</t>
         </is>
@@ -2168,29 +2148,29 @@
 Iron Man 2 · 2010</t>
         </is>
       </c>
-      <c r="D26" s="57" t="inlineStr">
+      <c r="D26" s="52" t="inlineStr">
         <is>
           <t>#4A87EE</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>电光钴蓝
 Spotlight Sapphire</t>
         </is>
       </c>
-      <c r="F26" s="58" t="inlineStr">
+      <c r="F26" s="53" t="inlineStr">
         <is>
           <t>#13151C</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>落幕玄黑
 After-Curtain Onyx</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr"/>
+      <c r="H26" s="9" t="inlineStr"/>
     </row>
     <row r="27" ht="54" customHeight="1">
       <c r="A27" s="4" t="n">
@@ -2201,41 +2181,41 @@
           <t>Kenny Waters</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>《定罪》
 Conviction · 2010</t>
         </is>
       </c>
-      <c r="D27" s="59" t="inlineStr">
-        <is>
-          <t>#D08A45</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>铁窗微光
-Barred Light</t>
-        </is>
-      </c>
-      <c r="F27" s="60" t="inlineStr">
+      <c r="D27" s="54" t="inlineStr">
+        <is>
+          <t>#7A8FA3</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>铁窗微蓝
+Barred Blue</t>
+        </is>
+      </c>
+      <c r="F27" s="55" t="inlineStr">
         <is>
           <t>#1C1E1F</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>囚室灰墙
 Cell Concrete</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr"/>
+      <c r="H27" s="9" t="inlineStr"/>
     </row>
     <row r="28" ht="54" customHeight="1">
-      <c r="A28" s="11" t="n">
+      <c r="A28" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Karl Fairhurst</t>
         </is>
@@ -2246,29 +2226,29 @@
 The Sitter · 2011</t>
         </is>
       </c>
-      <c r="D28" s="61" t="inlineStr">
-        <is>
-          <t>#E2537F</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>霓虹玫红
-Neon Magenta</t>
-        </is>
-      </c>
-      <c r="F28" s="62" t="inlineStr">
+      <c r="D28" s="56" t="inlineStr">
+        <is>
+          <t>#D15F82</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>烟熏眼影
+Smoky Kohl</t>
+        </is>
+      </c>
+      <c r="F28" s="57" t="inlineStr">
         <is>
           <t>#181320</t>
         </is>
       </c>
-      <c r="G28" s="14" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>地窖绒黑
 Basement Velvet</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr"/>
+      <c r="H28" s="9" t="inlineStr"/>
     </row>
     <row r="29" ht="54" customHeight="1">
       <c r="A29" s="4" t="n">
@@ -2279,41 +2259,41 @@
           <t>Billy Bickle</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>《七个神经病》
 Seven Psychopaths · 2012</t>
         </is>
       </c>
-      <c r="D29" s="63" t="inlineStr">
-        <is>
-          <t>#D63A33</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>方块J红
-Diamond Jack</t>
-        </is>
-      </c>
-      <c r="F29" s="64" t="inlineStr">
+      <c r="D29" s="58" t="inlineStr">
+        <is>
+          <t>#C94A1E</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>方块烈焰
+Diamond Blaze</t>
+        </is>
+      </c>
+      <c r="F29" s="59" t="inlineStr">
         <is>
           <t>#281208</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>沙漠焦土
 Scorched Desert</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr"/>
+      <c r="H29" s="9" t="inlineStr"/>
     </row>
     <row r="30" ht="54" customHeight="1">
-      <c r="A30" s="11" t="n">
+      <c r="A30" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Owen</t>
         </is>
@@ -2324,35 +2304,35 @@
 The Way Way Back · 2013</t>
         </is>
       </c>
-      <c r="D30" s="65" t="inlineStr">
+      <c r="D30" s="60" t="inlineStr">
         <is>
           <t>#35BFC9</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>滑梯翠蓝
 Waterslide Aqua</t>
         </is>
       </c>
-      <c r="F30" s="66" t="inlineStr">
+      <c r="F30" s="61" t="inlineStr">
         <is>
           <t>#15282E</t>
         </is>
       </c>
-      <c r="G30" s="14" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>氯味深池
 Chlorine Deep</t>
         </is>
       </c>
-      <c r="H30" s="16" t="inlineStr"/>
+      <c r="H30" s="9" t="inlineStr"/>
     </row>
     <row r="31" ht="54" customHeight="1">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>John Moon</t>
         </is>
@@ -2363,35 +2343,35 @@
 A Single Shot · 2013</t>
         </is>
       </c>
-      <c r="D31" s="67" t="inlineStr">
+      <c r="D31" s="62" t="inlineStr">
         <is>
           <t>#8FA0B0</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>孤枪冷雾蓝
 Lone Mist</t>
         </is>
       </c>
-      <c r="F31" s="68" t="inlineStr">
+      <c r="F31" s="63" t="inlineStr">
         <is>
           <t>#14181F</t>
         </is>
       </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>西弗州山夜
 Appalachian Dusk</t>
         </is>
       </c>
-      <c r="H31" s="16" t="inlineStr"/>
+      <c r="H31" s="9" t="inlineStr"/>
     </row>
     <row r="32" ht="54" customHeight="1">
-      <c r="A32" s="11" t="n">
+      <c r="A32" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Doug Varney</t>
         </is>
@@ -2402,29 +2382,29 @@
 Better Living Through Chemistry · 2014</t>
         </is>
       </c>
-      <c r="D32" s="69" t="inlineStr">
+      <c r="D32" s="64" t="inlineStr">
         <is>
           <t>#E6ECEA</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>处方白大褂
 Lab Coat</t>
         </is>
       </c>
-      <c r="F32" s="70" t="inlineStr">
+      <c r="F32" s="65" t="inlineStr">
         <is>
           <t>#1E1408</t>
         </is>
       </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>药瓶琥珀棕
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>药瓶陈皮棕
 Pill-Bottle Brown</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr"/>
+      <c r="H32" s="9" t="inlineStr"/>
     </row>
     <row r="33" ht="54" customHeight="1">
       <c r="A33" s="4" t="n">
@@ -2435,35 +2415,35 @@
           <t>Wayne</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>《十日编剧手册》
 Loitering with Intent · 2014</t>
         </is>
       </c>
-      <c r="D33" s="71" t="inlineStr">
-        <is>
-          <t>#C8A050</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>夏末琥珀
-Late Summer Amber</t>
-        </is>
-      </c>
-      <c r="F33" s="72" t="inlineStr">
+      <c r="D33" s="66" t="inlineStr">
+        <is>
+          <t>#C98868</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>陶土暖橘
+Terracotta Warm</t>
+        </is>
+      </c>
+      <c r="F33" s="67" t="inlineStr">
         <is>
           <t>#1E2418</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>退伍橄榄
 Old Olive</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr"/>
+      <c r="H33" s="9" t="inlineStr"/>
     </row>
     <row r="34" ht="54" customHeight="1">
       <c r="A34" s="4" t="n">
@@ -2474,35 +2454,35 @@
           <t>Craig</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>《迟来的告白》
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>《慢半拍》
 Laggies · 2014</t>
         </is>
       </c>
-      <c r="D34" s="73" t="inlineStr">
-        <is>
-          <t>#C89060</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>威士忌金
-Whisky Gold</t>
-        </is>
-      </c>
-      <c r="F34" s="74" t="inlineStr">
-        <is>
-          <t>#241A14</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>陈年皮革
-Aged Leather</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="inlineStr"/>
+      <c r="D34" s="68" t="inlineStr">
+        <is>
+          <t>#63788A</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>法务灰蓝
+Legal Slate Blue</t>
+        </is>
+      </c>
+      <c r="F34" s="69" t="inlineStr">
+        <is>
+          <t>#1C2228</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>停车场夜
+Strip-Mall Night</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr"/>
     </row>
     <row r="35" ht="54" customHeight="1">
       <c r="A35" s="4" t="n">
@@ -2513,35 +2493,35 @@
           <t>Eric Bowen</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>《鬼驱人》
 Poltergeist · 2015</t>
         </is>
       </c>
-      <c r="D35" s="75" t="inlineStr">
-        <is>
-          <t>#D8A24E</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>夜灯黄铜
-Nightlight Brass</t>
-        </is>
-      </c>
-      <c r="F35" s="76" t="inlineStr">
+      <c r="D35" s="70" t="inlineStr">
+        <is>
+          <t>#9FB8C9</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>荧屏冷光
+Static Glow</t>
+        </is>
+      </c>
+      <c r="F35" s="71" t="inlineStr">
         <is>
           <t>#1B1917</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>空房暮灰
 Empty-Room Grey</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr"/>
+      <c r="H35" s="9" t="inlineStr"/>
     </row>
     <row r="36" ht="54" customHeight="1">
       <c r="A36" s="4" t="n">
@@ -2552,152 +2532,152 @@
           <t>Francis Munch</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>《真命天子》
 Mr. Right · 2015</t>
         </is>
       </c>
-      <c r="D36" s="77" t="inlineStr">
+      <c r="D36" s="72" t="inlineStr">
         <is>
           <t>#E23B2E</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>丑角红鼻头
 Clown Nose</t>
         </is>
       </c>
-      <c r="F36" s="78" t="inlineStr">
+      <c r="F36" s="73" t="inlineStr">
         <is>
           <t>#14241A</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>小熊软糖绿
 Gummy Bear Green</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr"/>
+      <c r="H36" s="9" t="inlineStr"/>
     </row>
     <row r="37" ht="54" customHeight="1">
-      <c r="A37" s="11" t="n">
+      <c r="A37" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Don Verdean</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>《唐·维尔登》
+Don Verdean · 2015</t>
+        </is>
+      </c>
+      <c r="D37" s="74" t="inlineStr">
+        <is>
+          <t>#4FA0A0</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>圣物青绿
+Relic Turquoise</t>
+        </is>
+      </c>
+      <c r="F37" s="33" t="inlineStr">
+        <is>
+          <t>#1A1410</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>暮土玄褐
+Dusk Umber</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38" ht="54" customHeight="1">
+      <c r="A38" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Jason Dixon</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>《三块广告牌》
 Three Billboards Outside Ebbing, Missouri · 2017</t>
         </is>
       </c>
-      <c r="D37" s="79" t="inlineStr">
+      <c r="D38" s="75" t="inlineStr">
         <is>
           <t>#E2622A</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>重生焰橘
 Reborn Flame</t>
         </is>
       </c>
-      <c r="F37" s="80" t="inlineStr">
+      <c r="F38" s="76" t="inlineStr">
         <is>
           <t>#241015</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>焦烬玫瑰
 Charred Rose</t>
         </is>
       </c>
-      <c r="H37" s="16" t="inlineStr"/>
-    </row>
-    <row r="38" ht="54" customHeight="1">
-      <c r="A38" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="H38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39" ht="54" customHeight="1">
+      <c r="A39" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Colonel Silas Groves</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>《女先行者》
 Woman Walks Ahead · 2017</t>
         </is>
       </c>
-      <c r="D38" s="81" t="inlineStr">
+      <c r="D39" s="77" t="inlineStr">
         <is>
           <t>#8C3229</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>陈血锈红
 Dried Blood</t>
         </is>
       </c>
-      <c r="F38" s="82" t="inlineStr">
+      <c r="F39" s="78" t="inlineStr">
         <is>
           <t>#161A1F</t>
         </is>
       </c>
-      <c r="G38" s="14" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>边境暮雪
 Frontier Dusk</t>
         </is>
       </c>
-      <c r="H38" s="16" t="inlineStr"/>
-    </row>
-    <row r="39" ht="54" customHeight="1">
-      <c r="A39" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>Eddie</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>《蓝蜥蜴》
-Blue Iguana · 2018</t>
-        </is>
-      </c>
-      <c r="D39" s="83" t="inlineStr">
-        <is>
-          <t>#2E9FD4</t>
-        </is>
-      </c>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>蓝蜥宝石
-Iguana Jewel</t>
-        </is>
-      </c>
-      <c r="F39" s="84" t="inlineStr">
-        <is>
-          <t>#1A1F24</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>酒馆烟灰
-Tavern Smoke</t>
-        </is>
-      </c>
-      <c r="H39" s="16" t="inlineStr"/>
+      <c r="H39" s="9" t="inlineStr"/>
     </row>
     <row r="40" ht="54" customHeight="1">
       <c r="A40" s="4" t="n">
@@ -2705,38 +2685,38 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>George W. Bush</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>《副总统》
-Vice · 2018</t>
-        </is>
-      </c>
-      <c r="D40" s="85" t="inlineStr">
-        <is>
-          <t>#C98A3E</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>德州牛仔金
-Texan Tan</t>
-        </is>
-      </c>
-      <c r="F40" s="86" t="inlineStr">
-        <is>
-          <t>#16181E</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>总统西装夜
-Suit Navy</t>
-        </is>
-      </c>
-      <c r="H40" s="10" t="inlineStr"/>
+          <t>Eddie</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>《蓝蜥蜴》
+Blue Iguana · 2018</t>
+        </is>
+      </c>
+      <c r="D40" s="79" t="inlineStr">
+        <is>
+          <t>#2E9FD4</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>蓝蜥宝石
+Iguana Jewel</t>
+        </is>
+      </c>
+      <c r="F40" s="80" t="inlineStr">
+        <is>
+          <t>#1A1F24</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>酒馆烟灰
+Tavern Smoke</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr"/>
     </row>
     <row r="41" ht="54" customHeight="1">
       <c r="A41" s="4" t="n">
@@ -2744,38 +2724,38 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Captain Klenzendorf</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>《乔乔的异想世界》
-Jojo Rabbit · 2019</t>
-        </is>
-      </c>
-      <c r="D41" s="87" t="inlineStr">
-        <is>
-          <t>#D34338</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>夸张军装红
-Glam Tunic</t>
-        </is>
-      </c>
-      <c r="F41" s="88" t="inlineStr">
-        <is>
-          <t>#14241C</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>登台华服绿
-Costume Green</t>
-        </is>
-      </c>
-      <c r="H41" s="10" t="inlineStr"/>
+          <t>George W. Bush</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>《副总统》
+Vice · 2018</t>
+        </is>
+      </c>
+      <c r="D41" s="81" t="inlineStr">
+        <is>
+          <t>#C17F34</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>德州牛仔金
+Texan Tan</t>
+        </is>
+      </c>
+      <c r="F41" s="82" t="inlineStr">
+        <is>
+          <t>#16181E</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>总统西装夜
+Suit Navy</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr"/>
     </row>
     <row r="42" ht="54" customHeight="1">
       <c r="A42" s="4" t="n">
@@ -2783,38 +2763,38 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Watson Bryant</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>《理查德·朱维尔的哀歌》
-Richard Jewell · 2019</t>
-        </is>
-      </c>
-      <c r="D42" s="89" t="inlineStr">
-        <is>
-          <t>#C8783C</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>红土暖橘
-Georgia Clay</t>
-        </is>
-      </c>
-      <c r="F42" s="90" t="inlineStr">
-        <is>
-          <t>#1C1410</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>档案橡木
-Archive Oak</t>
-        </is>
-      </c>
-      <c r="H42" s="10" t="inlineStr"/>
+          <t>Captain Klenzendorf</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>《乔乔的异想世界》
+Jojo Rabbit · 2019</t>
+        </is>
+      </c>
+      <c r="D42" s="83" t="inlineStr">
+        <is>
+          <t>#9C3F2A</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>焦锈军装红
+Scorched Oxblood</t>
+        </is>
+      </c>
+      <c r="F42" s="84" t="inlineStr">
+        <is>
+          <t>#14241C</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>登台华服绿
+Costume Green</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr"/>
     </row>
     <row r="43" ht="54" customHeight="1">
       <c r="A43" s="4" t="n">
@@ -2822,38 +2802,38 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>C.P. "Clay" Ellis</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>《最佳敌人》
-The Best of Enemies · 2019</t>
-        </is>
-      </c>
-      <c r="D43" s="91" t="inlineStr">
-        <is>
-          <t>#B87A3E</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>焦糖小熊棕
-Caramel Bear</t>
-        </is>
-      </c>
-      <c r="F43" s="92" t="inlineStr">
-        <is>
-          <t>#161510</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>蝉鸣仲夏夜
-Cicada Nightfall</t>
-        </is>
-      </c>
-      <c r="H43" s="10" t="inlineStr"/>
+          <t>Watson Bryant</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>《理查德·朱维尔的哀歌》
+Richard Jewell · 2019</t>
+        </is>
+      </c>
+      <c r="D43" s="85" t="inlineStr">
+        <is>
+          <t>#7A9468</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>香烟灰绿
+Ashtray Sage</t>
+        </is>
+      </c>
+      <c r="F43" s="86" t="inlineStr">
+        <is>
+          <t>#1C1410</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>档案橡木
+Archive Oak</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr"/>
     </row>
     <row r="44" ht="54" customHeight="1">
       <c r="A44" s="4" t="n">
@@ -2861,38 +2841,38 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Mr. Wolf</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>《坏蛋联盟》
-The Bad Guys · 2022</t>
-        </is>
-      </c>
-      <c r="D44" s="93" t="inlineStr">
-        <is>
-          <t>#DFB23C</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>磁石黄金
-Magnet Gold</t>
-        </is>
-      </c>
-      <c r="F44" s="94" t="inlineStr">
-        <is>
-          <t>#14161D</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>狼影灰蓝
-Wolf Shadow</t>
-        </is>
-      </c>
-      <c r="H44" s="10" t="inlineStr"/>
+          <t>C.P. "Clay" Ellis</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>《最佳敌人》
+The Best of Enemies · 2019</t>
+        </is>
+      </c>
+      <c r="D44" s="87" t="inlineStr">
+        <is>
+          <t>#9C6F38</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>焦糖小熊棕
+Caramel Bear</t>
+        </is>
+      </c>
+      <c r="F44" s="88" t="inlineStr">
+        <is>
+          <t>#161510</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>蝉鸣仲夏夜
+Cicada Nightfall</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr"/>
     </row>
     <row r="45" ht="54" customHeight="1">
       <c r="A45" s="4" t="n">
@@ -2900,38 +2880,38 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Inspector Stoppard</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>《看他们如何逃之夭夭》
-See How They Run · 2022</t>
-        </is>
-      </c>
-      <c r="D45" s="95" t="inlineStr">
-        <is>
-          <t>#C7995A</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>旧照片暖褐
-Old Photograph</t>
-        </is>
-      </c>
-      <c r="F45" s="96" t="inlineStr">
-        <is>
-          <t>#1A1F2C</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>伦敦午夜蓝
-London Midnight</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="inlineStr"/>
+          <t>Mr. Wolf</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>《坏蛋联盟》
+The Bad Guys · 2022</t>
+        </is>
+      </c>
+      <c r="D45" s="89" t="inlineStr">
+        <is>
+          <t>#E0B840</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>磁石黄金
+Magnet Gold</t>
+        </is>
+      </c>
+      <c r="F45" s="90" t="inlineStr">
+        <is>
+          <t>#14161D</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>狼影灰蓝
+Wolf Shadow</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr"/>
     </row>
     <row r="46" ht="54" customHeight="1">
       <c r="A46" s="4" t="n">
@@ -2939,38 +2919,38 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Aidan Wilde</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>《阿盖尔:神秘特工》
-Argylle · 2024</t>
-        </is>
-      </c>
-      <c r="D46" s="97" t="inlineStr">
-        <is>
-          <t>#CDA24F</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>弹壳余温金
-Casing Gold</t>
-        </is>
-      </c>
-      <c r="F46" s="98" t="inlineStr">
-        <is>
-          <t>#15192A</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t>午夜枪管蓝
-Gunmetal Blue</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr"/>
+          <t>Inspector Stoppard</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>《看他们如何逃之夭夭》
+See How They Run · 2022</t>
+        </is>
+      </c>
+      <c r="D46" s="91" t="inlineStr">
+        <is>
+          <t>#E2C48F</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>旧照片暖褐
+Old Photograph</t>
+        </is>
+      </c>
+      <c r="F46" s="92" t="inlineStr">
+        <is>
+          <t>#1A1F2C</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>伦敦午夜蓝
+London Midnight</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr"/>
     </row>
     <row r="47" ht="54" customHeight="1">
       <c r="A47" s="4" t="n">
@@ -2978,44 +2958,44 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Don Verdean</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>《唐·维尔登》
-Don Verdean · 2015</t>
-        </is>
-      </c>
-      <c r="D47" s="99" t="inlineStr">
-        <is>
-          <t>#C69A4B</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>圣物流金
-Relic Gold</t>
-        </is>
-      </c>
-      <c r="F47" s="38" t="inlineStr">
-        <is>
-          <t>#1A1410</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>暮土玄褐
-Dusk Umber</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="inlineStr"/>
+          <t>Aidan Wilde</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>《阿盖尔:神秘特工》
+Argylle · 2024</t>
+        </is>
+      </c>
+      <c r="D47" s="93" t="inlineStr">
+        <is>
+          <t>#A8ADB8</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>枪管冷银光
+Gunmetal Silver</t>
+        </is>
+      </c>
+      <c r="F47" s="94" t="inlineStr">
+        <is>
+          <t>#15192A</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>午夜枪管蓝
+Gunmetal Blue</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr"/>
     </row>
     <row r="48" ht="54" customHeight="1">
-      <c r="A48" s="11" t="n">
+      <c r="A48" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>The Man from the Future</t>
         </is>
@@ -3026,29 +3006,29 @@
 Good Luck, Have Fun, Don't Die · 2025</t>
         </is>
       </c>
-      <c r="D48" s="100" t="inlineStr">
+      <c r="D48" s="95" t="inlineStr">
         <is>
           <t>#D460A0</t>
         </is>
       </c>
-      <c r="E48" s="14" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>故障玫红
 Glitch Magenta</t>
         </is>
       </c>
-      <c r="F48" s="101" t="inlineStr">
+      <c r="F48" s="96" t="inlineStr">
         <is>
           <t>#1A0E2A</t>
         </is>
       </c>
-      <c r="G48" s="14" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>荧光夜紫
 Neon Violet</t>
         </is>
       </c>
-      <c r="H48" s="16" t="inlineStr"/>
+      <c r="H48" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/sam_themes_palette_review.xlsx
+++ b/sam_themes_palette_review.xlsx
@@ -275,12 +275,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C17858"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00341524"/>
+        <fgColor rgb="00D2A24A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00350D1E"/>
       </patternFill>
     </fill>
     <fill>
@@ -385,12 +385,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C98868"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E2418"/>
+        <fgColor rgb="003F7A52"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002A1810"/>
       </patternFill>
     </fill>
     <fill>
@@ -682,7 +682,7 @@
     <xf numFmtId="0" fontId="8" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="40" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="40" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -748,7 +748,7 @@
     <xf numFmtId="0" fontId="8" fillId="61" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="62" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="62" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1649,7 +1649,7 @@
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>镜绯红
-Rouge Lens</t>
+Crimson Lens</t>
         </is>
       </c>
       <c r="F13" s="27" t="inlineStr">
@@ -1765,8 +1765,8 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>银灰猫眼
-Mauve Fox</t>
+          <t>紫雾榛眸
+Hazel Mauve</t>
         </is>
       </c>
       <c r="F16" s="33" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>黑貂皮大氅
+          <t>貂皮大氅黑
 Mink Black</t>
         </is>
       </c>
@@ -1994,24 +1994,24 @@
       </c>
       <c r="D22" s="44" t="inlineStr">
         <is>
-          <t>#C17858</t>
+          <t>#D2A24A</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>铜锈玫瑰
-Copper Rose</t>
+          <t>殖民地铜金
+Colonial Gilt</t>
         </is>
       </c>
       <c r="F22" s="45" t="inlineStr">
         <is>
-          <t>#341524</t>
+          <t>#350D1E</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>绒夜玫红
-Rose Velvet Night</t>
+          <t>海报品红夜
+Poster Magenta Night</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr"/>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>星尘墨夜
+          <t>苍穹墨夜
 Stardust Night</t>
         </is>
       </c>
@@ -2272,8 +2272,8 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>方块烈焰
-Diamond Blaze</t>
+          <t>方块J焰
+Jack of Diamonds</t>
         </is>
       </c>
       <c r="F29" s="59" t="inlineStr">
@@ -2423,24 +2423,24 @@
       </c>
       <c r="D33" s="66" t="inlineStr">
         <is>
-          <t>#C98868</t>
+          <t>#3F7A52</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>陶土暖橘
-Terracotta Warm</t>
+          <t>敞篷车绿
+Racing Green</t>
         </is>
       </c>
       <c r="F33" s="67" t="inlineStr">
         <is>
-          <t>#1E2418</t>
+          <t>#2A1810</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>退伍橄榄
-Old Olive</t>
+          <t>别墅夏夜
+Villa Summer Night</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr"/>
@@ -2974,8 +2974,8 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>枪管冷银光
-Gunmetal Silver</t>
+          <t>冷银弹壳光
+Casing Silver</t>
         </is>
       </c>
       <c r="F47" s="94" t="inlineStr">
